--- a/Practical3/Excel Sheets/Task 1.xlsx
+++ b/Practical3/Excel Sheets/Task 1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="62" documentId="8_{2A448505-1664-449C-BE3B-6EA1F8AE234E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9343D07D-A022-47B5-A69A-AB9A7CEB4ECB}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-1092" yWindow="1440" windowWidth="17280" windowHeight="9960" xr2:uid="{D1FF1C14-26E8-48FD-8176-7C1125D36F23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D1FF1C14-26E8-48FD-8176-7C1125D36F23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
